--- a/Satisfacao/Satisfacao-modelo.xlsx
+++ b/Satisfacao/Satisfacao-modelo.xlsx
@@ -96,7 +96,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Reclamação grave ou repetida vira registro de não conformidade, com análise de causa.</t>
+          <t xml:space="preserve">Reclamação procedente é não conformidade e recebe correção. A grave ou repetida abre registro de não conformidade, com análise de causa.</t>
         </r>
       </text>
     </comment>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Prazos</t>
   </si>
   <si>
-    <t xml:space="preserve">Resposta em até 2 dias úteis e solução em até 10 dias, neste modelo. A organização define os seus.</t>
+    <t xml:space="preserve">Primeira resposta em até 2 dias úteis e solução em até 10 dias, neste modelo. A organização define os seus.</t>
   </si>
   <si>
     <t xml:space="preserve">Ordem recomendada de preenchimento</t>
@@ -258,7 +258,7 @@
     <t xml:space="preserve">Reclamações</t>
   </si>
   <si>
-    <t xml:space="preserve">Até 30 reclamações. Calcula o prazo de resposta e a situação de cada uma, e conta os motivos.</t>
+    <t xml:space="preserve">Até 30 reclamações. Calcula o prazo da primeira resposta e a situação de cada uma, e conta os motivos.</t>
   </si>
   <si>
     <t xml:space="preserve">Painel</t>
@@ -441,7 +441,7 @@
     <t xml:space="preserve">Promotores, neutros e detratores</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma linha por reclamação, de qualquer canal. O prazo de resposta e a situação são calculados pelas datas.</t>
+    <t xml:space="preserve">Uma linha por reclamação, de qualquer canal. O prazo da primeira resposta e a situação são calculados pelas datas.</t>
   </si>
   <si>
     <t xml:space="preserve">Canal</t>
@@ -636,7 +636,7 @@
     <t xml:space="preserve">Os motivos das reclamações e das notas baixas são agrupados e analisados.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reclamação grave ou repetida vira não conformidade, com análise de causa.</t>
+    <t xml:space="preserve">Reclamação procedente é tratada como não conformidade, com correção, e a grave ou repetida tem análise de causa.</t>
   </si>
   <si>
     <t xml:space="preserve">Os indicadores de satisfação têm meta e entram no painel da organização.</t>
@@ -1530,11 +1530,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="54958483"/>
-        <c:axId val="62829769"/>
+        <c:axId val="80376527"/>
+        <c:axId val="76708675"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54958483"/>
+        <c:axId val="80376527"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1566,7 +1566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62829769"/>
+        <c:crossAx val="76708675"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1574,7 +1574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62829769"/>
+        <c:axId val="76708675"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1614,7 +1614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54958483"/>
+        <c:crossAx val="80376527"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1963,7 +1963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
         <v>42</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Satisfacao/Satisfacao-modelo.xlsx
+++ b/Satisfacao/Satisfacao-modelo.xlsx
@@ -1530,11 +1530,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="80376527"/>
-        <c:axId val="76708675"/>
+        <c:axId val="86890557"/>
+        <c:axId val="68276159"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80376527"/>
+        <c:axId val="86890557"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1566,7 +1566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76708675"/>
+        <c:crossAx val="68276159"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1574,7 +1574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76708675"/>
+        <c:axId val="68276159"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1614,7 +1614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80376527"/>
+        <c:crossAx val="86890557"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
